--- a/backend/templates/5.6_Template.xlsx
+++ b/backend/templates/5.6_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91981\OneDrive\Documents\ifqe\criteria 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D903F88D-1273-4526-9AD1-DA6A14B2E885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D58DEE45-7972-4B07-B5FB-F6F482DC2307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,20 +25,28 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t xml:space="preserve"> Documents to be Uploaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Evidence Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   5.6 No. of Books procured in the library</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.Approval document for books procurement during
- assessment year
- 2.Verified list of books procured from library</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>S.No.</t>
+  </si>
+  <si>
+    <t>5.8 School membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Name of
+ Membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Membership ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Validity Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Renewal Date</t>
+  </si>
+  <si>
+    <t>Evidence Link (Certificate/Proof)</t>
   </si>
   <si>
     <t>to be uploaded on portal</t>
@@ -48,7 +56,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,7 +66,22 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -116,6 +139,17 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -146,21 +180,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,36 +482,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="57.88671875" customWidth="1"/>
-    <col min="2" max="2" width="56" customWidth="1"/>
+    <col min="1" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" customWidth="1"/>
+    <col min="6" max="6" width="34.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="8"/>
     </row>
-    <row r="2" spans="1:2" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>4</v>
+    <row r="3" spans="1:6" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>